--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ88"/>
+  <dimension ref="A1:AZ89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7861,53 +7861,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>106197313</v>
+        <v>136749242</v>
       </c>
       <c r="B63" t="n">
-        <v>57950</v>
+        <v>93440</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, Vg</t>
+          <t>Gäddevadsbäcken, Gäddevadsbäcken, Vg</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>338494</v>
+        <v>338729</v>
       </c>
       <c r="R63" t="n">
-        <v>6433149</v>
+        <v>6433099</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7931,22 +7926,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7961,24 +7956,24 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106197313</t>
+          <t>https://artportalen.se/Sighting/136749242</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112016525</v>
+        <v>106197313</v>
       </c>
       <c r="B64" t="n">
         <v>57950</v>
@@ -8006,28 +8001,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Röserna, norr om, Vg</t>
+          <t>Gäddevadsbäcken, Vg</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>339733</v>
+        <v>338494</v>
       </c>
       <c r="R64" t="n">
-        <v>6433042</v>
+        <v>6433149</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8051,17 +8043,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-01-28</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Spår efter spillkråka vid stambasen hos tall i sydvänd brant.</t>
+          <t>2023-01-28</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8072,38 +8069,28 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Blandskog i branter</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Tall och ek i sydvänd brant</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112016525</t>
+          <t>https://artportalen.se/Sighting/106197313</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112236100</v>
+        <v>112016525</v>
       </c>
       <c r="B65" t="n">
         <v>57950</v>
@@ -8142,14 +8129,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Röserna, norr om, Vg</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>338598</v>
+        <v>339733</v>
       </c>
       <c r="R65" t="n">
-        <v>6433091</v>
+        <v>6433042</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8176,17 +8163,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Spår efter spillkråka som födosökt vid stambasen på en högstubbe</t>
+          <t>Spår efter spillkråka vid stambasen hos tall i sydvänd brant.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8197,6 +8184,16 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Tall och ek i sydvänd brant</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8212,13 +8209,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112236100</t>
+          <t>https://artportalen.se/Sighting/112016525</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112319668</v>
+        <v>112236100</v>
       </c>
       <c r="B66" t="n">
         <v>57950</v>
@@ -8251,20 +8248,20 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, söder om, Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>339565</v>
+        <v>338598</v>
       </c>
       <c r="R66" t="n">
-        <v>6433114</v>
+        <v>6433091</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8291,17 +8288,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Vid basen av död gran mm</t>
+          <t>Spår efter spillkråka som födosökt vid stambasen på en högstubbe</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8316,24 +8313,24 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112319668</t>
+          <t>https://artportalen.se/Sighting/112236100</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120110497</v>
+        <v>112319668</v>
       </c>
       <c r="B67" t="n">
         <v>57950</v>
@@ -8366,20 +8363,20 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mickelsdamm, sydost om, Vg</t>
+          <t>Gäddevadsbäcken, söder om, Vg</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>339514</v>
+        <v>339565</v>
       </c>
       <c r="R67" t="n">
-        <v>6433090</v>
+        <v>6433114</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8406,17 +8403,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
+          <t>Vid basen av död gran mm</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8431,27 +8428,27 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120110497</t>
+          <t>https://artportalen.se/Sighting/112319668</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112118159</v>
+        <v>120110497</v>
       </c>
       <c r="B68" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8459,43 +8456,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, Vg</t>
+          <t>Mickelsdamm, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>338583</v>
+        <v>339514</v>
       </c>
       <c r="R68" t="n">
-        <v>6433160</v>
+        <v>6433090</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8522,17 +8518,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>ca 10 mm brett spår. På senvuxen,klen gran. Mycket kåda.</t>
+          <t>Spår efter födosök av spillkråka i en 1,5 m hög högstubbe.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8541,34 +8537,33 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112118159</t>
+          <t>https://artportalen.se/Sighting/120110497</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127820719</v>
+        <v>112118159</v>
       </c>
       <c r="B69" t="n">
-        <v>57947</v>
+        <v>5179</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8576,51 +8571,46 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102977</v>
+        <v>100526</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+          <t>Gäddevadsbäcken, Vg</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>338683</v>
+        <v>338583</v>
       </c>
       <c r="R69" t="n">
-        <v>6433100</v>
+        <v>6433160</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8644,12 +8634,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>ca 10 mm brett spår. På senvuxen,klen gran. Mycket kåda.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8658,33 +8653,34 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127820719</t>
+          <t>https://artportalen.se/Sighting/112118159</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>112319655</v>
+        <v>127820719</v>
       </c>
       <c r="B70" t="n">
-        <v>58327</v>
+        <v>57947</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8692,21 +8688,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8714,27 +8710,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, söder om, Vg</t>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>339683</v>
+        <v>338683</v>
       </c>
       <c r="R70" t="n">
-        <v>6433112</v>
+        <v>6433100</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8758,22 +8756,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8788,24 +8776,24 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112319655</t>
+          <t>https://artportalen.se/Sighting/127820719</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>112411685</v>
+        <v>112319655</v>
       </c>
       <c r="B71" t="n">
         <v>58327</v>
@@ -8833,24 +8821,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Gäddevadsbäcken, söder om, Vg</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>338745</v>
+        <v>339683</v>
       </c>
       <c r="R71" t="n">
-        <v>6433077</v>
+        <v>6433112</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8874,12 +8870,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8894,24 +8900,24 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112411685</t>
+          <t>https://artportalen.se/Sighting/112319655</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>112431347</v>
+        <v>112411685</v>
       </c>
       <c r="B72" t="n">
         <v>58327</v>
@@ -8939,32 +8945,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>338735</v>
+        <v>338745</v>
       </c>
       <c r="R72" t="n">
-        <v>6433080</v>
+        <v>6433077</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8988,27 +8986,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Minst 2 ex.</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9023,65 +9006,77 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112431347</t>
+          <t>https://artportalen.se/Sighting/112411685</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127817601</v>
+        <v>112431347</v>
       </c>
       <c r="B73" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+          <t>Gäddevadsbäcken, Vg</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>338727</v>
+        <v>338735</v>
       </c>
       <c r="R73" t="n">
-        <v>6433070</v>
+        <v>6433080</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9105,22 +9100,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Minst 2 ex.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9135,24 +9135,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127817601</t>
+          <t>https://artportalen.se/Sighting/112431347</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129026915</v>
+        <v>127817601</v>
       </c>
       <c r="B74" t="n">
         <v>58114</v>
@@ -9180,29 +9180,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>338675</v>
+        <v>338727</v>
       </c>
       <c r="R74" t="n">
-        <v>6433103</v>
+        <v>6433070</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9226,22 +9217,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9267,63 +9258,63 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129026915</t>
+          <t>https://artportalen.se/Sighting/127817601</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>112118162</v>
+        <v>129026915</v>
       </c>
       <c r="B75" t="n">
-        <v>5199</v>
+        <v>58114</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken, Vg</t>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>338583</v>
+        <v>338675</v>
       </c>
       <c r="R75" t="n">
-        <v>6433160</v>
+        <v>6433103</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9347,17 +9338,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rätt mycket spår på nedre del av senvuxen gran. Även bronshjon-gnag på samma träd.</t>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9366,31 +9362,30 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112118162</t>
+          <t>https://artportalen.se/Sighting/129026915</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>112431338</v>
+        <v>112118162</v>
       </c>
       <c r="B76" t="n">
         <v>5199</v>
@@ -9434,10 +9429,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>338710</v>
+        <v>338583</v>
       </c>
       <c r="R76" t="n">
-        <v>6433103</v>
+        <v>6433160</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9464,17 +9459,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>I senvuxen, klen gran.</t>
+          <t>Rätt mycket spår på nedre del av senvuxen gran. Även bronshjon-gnag på samma träd.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9501,16 +9496,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112431338</t>
+          <t>https://artportalen.se/Sighting/112118162</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>98803458</v>
+        <v>112431338</v>
       </c>
       <c r="B77" t="n">
-        <v>97983</v>
+        <v>5199</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9518,41 +9513,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Slereboåns dalgångs NR, Vg</t>
+          <t>Gäddevadsbäcken, Vg</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>338502</v>
+        <v>338710</v>
       </c>
       <c r="R77" t="n">
-        <v>6433126</v>
+        <v>6433103</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9576,12 +9576,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2022-02-27</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2022-02-27</t>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>I senvuxen, klen gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9597,24 +9602,24 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98803458</t>
+          <t>https://artportalen.se/Sighting/112431338</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128623143</v>
+        <v>98803458</v>
       </c>
       <c r="B78" t="n">
         <v>97983</v>
@@ -9642,24 +9647,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
+          <t>Slereboåns dalgångs NR, Vg</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>338866</v>
+        <v>338502</v>
       </c>
       <c r="R78" t="n">
-        <v>6433122</v>
+        <v>6433126</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9683,22 +9688,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>18:12</t>
+          <t>2022-02-27</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>18:12</t>
+          <t>2022-02-27</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9707,30 +9702,31 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128623143</t>
+          <t>https://artportalen.se/Sighting/98803458</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128623459</v>
+        <v>128623143</v>
       </c>
       <c r="B79" t="n">
         <v>97983</v>
@@ -9760,7 +9756,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9769,13 +9765,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>338878</v>
+        <v>338866</v>
       </c>
       <c r="R79" t="n">
-        <v>6433141</v>
+        <v>6433122</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9804,7 +9800,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9814,7 +9810,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9840,13 +9836,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128623459</t>
+          <t>https://artportalen.se/Sighting/128623143</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129025873</v>
+        <v>128623459</v>
       </c>
       <c r="B80" t="n">
         <v>97983</v>
@@ -9876,22 +9872,22 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mickelsdamm, Mickelsdamm, Vg</t>
+          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>338669</v>
+        <v>338878</v>
       </c>
       <c r="R80" t="n">
         <v>6433141</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9915,22 +9911,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9956,16 +9952,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129025873</t>
+          <t>https://artportalen.se/Sighting/128623459</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>112234897</v>
+        <v>129025873</v>
       </c>
       <c r="B81" t="n">
-        <v>101326</v>
+        <v>97983</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9973,42 +9969,38 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Mickelsdamm, Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>338737</v>
+        <v>338669</v>
       </c>
       <c r="R81" t="n">
-        <v>6433098</v>
+        <v>6433141</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10035,17 +10027,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Även yngre träd. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Växte 2 m nordväst om den fjälliga taggsvampen.</t>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10054,34 +10051,33 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112234897</t>
+          <t>https://artportalen.se/Sighting/129025873</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128621998</v>
+        <v>112234897</v>
       </c>
       <c r="B82" t="n">
-        <v>97975</v>
+        <v>101326</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10089,38 +10085,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>224361</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>338883</v>
+        <v>338737</v>
       </c>
       <c r="R82" t="n">
-        <v>6433164</v>
+        <v>6433098</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10147,22 +10147,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>17:32</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>17:32</t>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Även yngre träd. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Växte 2 m nordväst om den fjälliga taggsvampen.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10171,30 +10166,31 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128621998</t>
+          <t>https://artportalen.se/Sighting/112234897</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128622113</v>
+        <v>128621998</v>
       </c>
       <c r="B83" t="n">
         <v>97975</v>
@@ -10224,26 +10220,22 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>338884</v>
+        <v>338883</v>
       </c>
       <c r="R83" t="n">
-        <v>6433165</v>
+        <v>6433164</v>
       </c>
       <c r="S83" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10272,7 +10264,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10282,7 +10274,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10291,7 +10283,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10309,13 +10300,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128622113</t>
+          <t>https://artportalen.se/Sighting/128621998</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128622404</v>
+        <v>128622113</v>
       </c>
       <c r="B84" t="n">
         <v>97975</v>
@@ -10345,9 +10336,13 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
@@ -10357,10 +10352,10 @@
         <v>338884</v>
       </c>
       <c r="R84" t="n">
-        <v>6433164</v>
+        <v>6433165</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10389,7 +10384,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10399,7 +10394,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10408,6 +10403,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -10425,16 +10421,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128622404</t>
+          <t>https://artportalen.se/Sighting/128622113</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>112411635</v>
+        <v>128622404</v>
       </c>
       <c r="B85" t="n">
-        <v>80992</v>
+        <v>97975</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10442,37 +10438,38 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>230185</v>
+        <v>224361</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Gäddevadsbäcken , Gäddevadsbäcken , Vg</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>339209</v>
+        <v>338884</v>
       </c>
       <c r="R85" t="n">
-        <v>6433092</v>
+        <v>6433164</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10499,17 +10496,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Växte på en ensam, medelgrov hassel i en mossig granskog med inslag av tall och björk. Den växer i sluttningen upp mot en lite mer talldominerad del av skogen, d v s där granskogen övergår till att bli mer uppblandad med tall och björk. Lite blockigt vid hasseln också.</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10518,31 +10520,30 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112411635</t>
+          <t>https://artportalen.se/Sighting/128622404</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112411671</v>
+        <v>112411635</v>
       </c>
       <c r="B86" t="n">
         <v>80992</v>
@@ -10576,14 +10577,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Röserna, norr om, Vg</t>
+          <t>Mickelsdamm, söder om, Vg</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>339623</v>
+        <v>339209</v>
       </c>
       <c r="R86" t="n">
-        <v>6433082</v>
+        <v>6433092</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10620,7 +10621,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Växte på en medelgrov ek strax ovanför den sydvända branten.</t>
+          <t>Växte på en ensam, medelgrov hassel i en mossig granskog med inslag av tall och björk. Den växer i sluttningen upp mot en lite mer talldominerad del av skogen, d v s där granskogen övergår till att bli mer uppblandad med tall och björk. Lite blockigt vid hasseln också.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10647,13 +10648,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112411671</t>
+          <t>https://artportalen.se/Sighting/112411635</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112612655</v>
+        <v>112411671</v>
       </c>
       <c r="B87" t="n">
         <v>80992</v>
@@ -10691,10 +10692,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>339754</v>
+        <v>339623</v>
       </c>
       <c r="R87" t="n">
-        <v>6433067</v>
+        <v>6433082</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10721,17 +10722,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Växte på en av tre klena ekar som växte ihop.</t>
+          <t>Växte på en medelgrov ek strax ovanför den sydvända branten.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10758,62 +10759,54 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112612655</t>
+          <t>https://artportalen.se/Sighting/112411671</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>112234040</v>
+        <v>112612655</v>
       </c>
       <c r="B88" t="n">
-        <v>87099</v>
+        <v>80992</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>249278</v>
+        <v>230185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Mickelsdamm, söder om, Vg</t>
+          <t>Röserna, norr om, Vg</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>338742</v>
+        <v>339754</v>
       </c>
       <c r="R88" t="n">
-        <v>6433095</v>
+        <v>6433067</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10840,17 +10833,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen.</t>
+          <t>Växte på en av tre klena ekar som växte ihop.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10876,6 +10869,125 @@
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112612655</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>112234040</v>
+      </c>
+      <c r="B89" t="n">
+        <v>87099</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>338742</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6433095</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Växte i en granskog med medelgrov gran och inslag av medelgrov tall. Tydligt kalkpåverkat med flera kalkgynnade arter. Hotspot med naturvårdsintressanta arter. Blåsippa växte på platsen.</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112234040</t>
         </is>
@@ -10970,6 +11082,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -7864,7 +7864,7 @@
         <v>136749242</v>
       </c>
       <c r="B63" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -7864,7 +7864,7 @@
         <v>136749242</v>
       </c>
       <c r="B63" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -7864,7 +7864,7 @@
         <v>136749242</v>
       </c>
       <c r="B63" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -7864,7 +7864,7 @@
         <v>136749242</v>
       </c>
       <c r="B63" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -7864,7 +7864,7 @@
         <v>136749242</v>
       </c>
       <c r="B63" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -7864,7 +7864,7 @@
         <v>136749242</v>
       </c>
       <c r="B63" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -7864,7 +7864,7 @@
         <v>136749242</v>
       </c>
       <c r="B63" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -7864,7 +7864,7 @@
         <v>136749242</v>
       </c>
       <c r="B63" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -7864,7 +7864,7 @@
         <v>136749242</v>
       </c>
       <c r="B63" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -7864,7 +7864,7 @@
         <v>136749242</v>
       </c>
       <c r="B63" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -7864,7 +7864,7 @@
         <v>136749242</v>
       </c>
       <c r="B63" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -7864,7 +7864,7 @@
         <v>136749242</v>
       </c>
       <c r="B63" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 36673-2023 artfynd.xlsx
+++ b/artfynd/A 36673-2023 artfynd.xlsx
@@ -7864,7 +7864,7 @@
         <v>136749242</v>
       </c>
       <c r="B63" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
